--- a/비용 정리_260702.xlsx
+++ b/비용 정리_260702.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bkahn/Library/Mobile Documents/com~apple~CloudDocs/0. 사업/1. 결산/Deployment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF9E251-E1F0-3F4A-932C-75E7399DDFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE58809-A86E-2244-A0F8-75258A364B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{22CEC514-C066-E441-9C92-ED07EE8853CA}"/>
   </bookViews>
@@ -1534,7 +1534,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="159">
   <si>
     <t>수익</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2069,6 +2069,18 @@
   <si>
     <t>Jina</t>
   </si>
+  <si>
+    <t>법인 안병규 입금</t>
+  </si>
+  <si>
+    <t>개인사업자 입금</t>
+  </si>
+  <si>
+    <t>법인으로 송금</t>
+  </si>
+  <si>
+    <t>법인 대출</t>
+  </si>
 </sst>
 </file>
 
@@ -2079,7 +2091,7 @@
     <numFmt numFmtId="165" formatCode="###,##0"/>
     <numFmt numFmtId="166" formatCode="#,###"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2141,12 +2153,6 @@
       <name val="pd"/>
       <family val="2"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3331,13 +3337,11 @@
     <col min="20" max="21" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.1640625" style="4" customWidth="1"/>
     <col min="23" max="23" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="14.1640625" style="4" customWidth="1"/>
-    <col min="27" max="27" width="14.1640625" style="4" hidden="1" customWidth="1"/>
+    <col min="24" max="27" width="14.1640625" style="4" customWidth="1"/>
     <col min="28" max="28" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="13.1640625" style="4" customWidth="1"/>
     <col min="30" max="30" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.1640625" style="4" hidden="1" customWidth="1"/>
-    <col min="32" max="33" width="13.1640625" style="4" customWidth="1"/>
+    <col min="31" max="33" width="13.1640625" style="4" customWidth="1"/>
     <col min="34" max="34" width="12.5" style="4" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="14" style="4" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="13.1640625" style="4" hidden="1" customWidth="1"/>
@@ -3457,13 +3461,13 @@
         <v>2</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="AF1" s="4" t="s">
         <v>85</v>
@@ -3544,7 +3548,7 @@
         <v>86</v>
       </c>
       <c r="BF1" s="4" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="BG1" s="4" t="s">
         <v>94</v>
@@ -29990,7 +29994,7 @@
         <v>57</v>
       </c>
       <c r="BY33">
-        <f t="shared" ref="BY32:BY33" si="68">BW33*0.1</f>
+        <f t="shared" ref="BY33" si="68">BW33*0.1</f>
         <v>25.5</v>
       </c>
       <c r="BZ33">
@@ -31392,7 +31396,7 @@
         <v>20</v>
       </c>
       <c r="BY45">
-        <f t="shared" ref="BY45:BY46" si="96">BW45*0.1</f>
+        <f t="shared" ref="BY45" si="96">BW45*0.1</f>
         <v>22</v>
       </c>
       <c r="BZ45">

--- a/비용 정리_260702.xlsx
+++ b/비용 정리_260702.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bkahn/Library/Mobile Documents/com~apple~CloudDocs/0. 사업/1. 결산/Deployment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F453F6-E68C-FD4E-B85F-520FF80FC238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092CB5B0-3541-5549-8C37-E611FC0635E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{22CEC514-C066-E441-9C92-ED07EE8853CA}"/>
   </bookViews>
@@ -3340,7 +3340,9 @@
     <col min="20" max="21" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.1640625" style="4" customWidth="1"/>
     <col min="23" max="23" width="14.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="14.1640625" style="4" customWidth="1"/>
+    <col min="24" max="26" width="14.1640625" style="4" customWidth="1"/>
+    <col min="27" max="27" width="17.1640625" style="4" customWidth="1"/>
+    <col min="28" max="28" width="14.1640625" style="4" customWidth="1"/>
     <col min="29" max="29" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="13.1640625" style="4" customWidth="1"/>
     <col min="31" max="31" width="18.33203125" style="4" bestFit="1" customWidth="1"/>

--- a/비용 정리_260702.xlsx
+++ b/비용 정리_260702.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bkahn/Library/Mobile Documents/com~apple~CloudDocs/0. 사업/1. 결산/Deployment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092CB5B0-3541-5549-8C37-E611FC0635E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A8FB94-D2ED-EB42-9B68-A2BA00E8A251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{22CEC514-C066-E441-9C92-ED07EE8853CA}"/>
   </bookViews>
